--- a/jogos_2024-12-25.xlsx
+++ b/jogos_2024-12-25.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="M3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.95</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
         <v>2.5</v>
@@ -856,25 +856,25 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '62']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '47']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45651.5</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chabab Mohammedia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.2</v>
       </c>
-      <c r="O4" t="n">
-        <v>13</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="V4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['79', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.14</v>
+        <v>2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45651.5</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,16 +1030,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Chabab Mohammedia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>2</v>
@@ -1048,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75</v>
+        <v>1.2</v>
       </c>
       <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
         <v>2.6</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X5" t="n">
         <v>4</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y5" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['53', '62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['25', '47']</t>
+          <t>['79', '90+2']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>3.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.57</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45651.5</v>
